--- a/artfynd/A 62316-2023 artfynd.xlsx
+++ b/artfynd/A 62316-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY8"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>79388321</v>
+        <v>79388309</v>
       </c>
       <c r="B2" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80461</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>796383.4571893902</v>
+        <v>796371</v>
       </c>
       <c r="R2" t="n">
-        <v>7234943.935786725</v>
+        <v>7235223</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,24 +743,9 @@
           <t>2019-07-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -792,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>79388309</v>
+        <v>79388321</v>
       </c>
       <c r="B3" t="n">
-        <v>78596</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>796370.7192447821</v>
+        <v>796383</v>
       </c>
       <c r="R3" t="n">
-        <v>7235222.928890905</v>
+        <v>7234944</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,19 +840,14 @@
           <t>2019-07-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2019-07-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -907,12 +877,7 @@
         <v>79388322</v>
       </c>
       <c r="B4" t="n">
-        <v>56395</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -944,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>796389.5087123053</v>
+        <v>796390</v>
       </c>
       <c r="R4" t="n">
-        <v>7234947.087749531</v>
+        <v>7234947</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -977,19 +942,9 @@
           <t>2019-07-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1021,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>79388320</v>
+        <v>79388318</v>
       </c>
       <c r="B5" t="n">
-        <v>5135</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5179</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105930</v>
+        <v>100526</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vågbandad barkbock</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Semanotus undatus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>796373.4030777441</v>
+        <v>796372</v>
       </c>
       <c r="R5" t="n">
-        <v>7234972.184145518</v>
+        <v>7234978</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,19 +1044,9 @@
           <t>2019-07-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1136,12 +1076,7 @@
         <v>79388319</v>
       </c>
       <c r="B6" t="n">
-        <v>5107</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1173,10 +1108,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>796434.066380241</v>
+        <v>796434</v>
       </c>
       <c r="R6" t="n">
-        <v>7235061.385731049</v>
+        <v>7235061</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,19 +1141,9 @@
           <t>2019-07-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1250,15 +1175,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>79388327</v>
+        <v>79388320</v>
       </c>
       <c r="B7" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>5199</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1266,19 +1186,23 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>223597</v>
+        <v>105930</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vågbandad barkbock</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr"/>
+          <t>Semanotus undatus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1286,10 +1210,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>796504.8876121365</v>
+        <v>796373</v>
       </c>
       <c r="R7" t="n">
-        <v>7235176.199695516</v>
+        <v>7234972</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1319,19 +1243,9 @@
           <t>2019-07-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1358,15 +1272,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>79388318</v>
+        <v>79388324</v>
       </c>
       <c r="B8" t="n">
-        <v>5113</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1374,23 +1283,19 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100526</v>
+        <v>223597</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1398,10 +1303,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>796371.5941201299</v>
+        <v>796419</v>
       </c>
       <c r="R8" t="n">
-        <v>7234977.514835686</v>
+        <v>7235211</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1431,19 +1336,9 @@
           <t>2019-07-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2019-07-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,6 +1362,99 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>79388327</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99038</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>223597</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Jungfru marie nycklar</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Källbomark, Vb</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>796505</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7235176</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Byske</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2019-07-29</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2019-07-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 62316-2023 artfynd.xlsx
+++ b/artfynd/A 62316-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388309</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388321</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388322</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388318</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388319</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1269,6 +1299,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388320</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1362,6 +1397,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388324</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1455,8 +1495,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79388327</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>